--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -624,13 +624,13 @@
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -680,13 +680,13 @@
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -807,26 +807,16 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Bullet</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>子弹飞行物用的属性集</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" t="n">
@@ -836,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -845,7 +835,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -853,17 +843,17 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -879,28 +869,146 @@
     <row r="16">
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="F16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
+      <c r="E17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
+      <c r="E18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+      <c r="B19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Bullet</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>投射物通用属性集</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="n"/>
